--- a/models/BLK_DCF_Model_Hawkins_Holdings_2026.xlsx
+++ b/models/BLK_DCF_Model_Hawkins_Holdings_2026.xlsx
@@ -9,11 +9,12 @@
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Income Statement" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="FCF Bridge" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="WACC Calculator" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="DCF Valuation" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Sensitivity Tables" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Income Statement" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="FCF Bridge" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="WACC Calculator" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="DCF Valuation" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sensitivity Tables" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="245">
   <si>
     <t xml:space="preserve">BlackRock, Inc. (NYSE: BLK)</t>
   </si>
@@ -111,10 +112,10 @@
     <t xml:space="preserve">MODEL NAVIGATION</t>
   </si>
   <si>
-    <t xml:space="preserve">Sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab Code</t>
+    <t xml:space="preserve">Assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSOT | Street consensus + HH DCF overlays | All estimates link here</t>
   </si>
   <si>
     <t xml:space="preserve">Description</t>
@@ -168,6 +169,180 @@
     <t xml:space="preserve">DISCLAIMER: This model is prepared for the Perplexity Pitch Contest and is not financial advice. Sources: BlackRock Q4 2025 Earnings Release (Jan 15, 2026), SEC 10-K filings, StockAnalysis.com, GuruFocus, AlphaSpread, Yahoo Finance consensus estimates.</t>
   </si>
   <si>
+    <t xml:space="preserve">BlackRock (BLK) — DCF Model Assumptions  |  Single Source of Truth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All estimate cells in the model read from this sheet via green cross-sheet links. BLUE cells = editable inputs. BLACK cells = formulas. GREEN cells = cross-sheet references. Last updated: April 04, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source Tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Source &amp; URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCK A — STREET CONSENSUS ESTIMATES  (FY2026E)  |  Update when consensus revises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street FY26 Revenue Consensus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STREET_REV_FY26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SimplyWallSt / SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SimplyWallSt 10-analyst avg $27,774M (Dec 2025); Seeking Alpha ~$27,920M; https://simplywall.st/stocks/us/diversified-financials/nyse-blk/blackrock/future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street FY27 Revenue Consensus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STREET_REV_FY27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StockAnalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StockAnalysis 20-analyst avg $31,490M; https://stockanalysis.com/stocks/blk/forecast/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street FY26 GAAP Diluted EPS Consensus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STREET_GAAP_EPS_FY26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StockAnalysis 20-analyst consensus $54.95; https://stockanalysis.com/stocks/blk/forecast/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street FY26 Adjusted EPS Consensus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STREET_ADJ_EPS_FY26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FactSet / Visible Alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User-specified $56.84 (FactSet/Visible Alpha consensus); cross-check: StockAnalysis $54.95, SA ~$54.14, SimplyWallSt implied ~$53. NOTE: $56.84 represents a higher-quality sell-side trim. Update as consensus evolves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street FY27 Adjusted EPS Consensus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STREET_ADJ_EPS_FY27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StockAnalysis 20-analyst consensus $62.53; https://stockanalysis.com/stocks/blk/forecast/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCK B — BASE-CASE DCF REVENUE ASSUMPTIONS  |  Hawkins Holdings analytical overlay above street consensus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base-Case DCF Revenue Assumption — FY26E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF_REV_FY26_BASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH Overlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH base-case set 2.6% above SimplyWallSt street ($27,774M) and equal to StockAnalysis 20-analyst avg ($28,480M). Rationale: Aladdin ACV ramp + GIP management fees not fully reflected in shorter-coverage SA sample. https://stockanalysis.com/stocks/blk/forecast/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base-Case DCF Revenue Assumption — FY27E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF_REV_FY27_BASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH = Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY27E base equals StockAnalysis consensus; no overlay applied — less analyst divergence. https://stockanalysis.com/stocks/blk/forecast/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear-Case DCF Revenue — FY26E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF_REV_FY26_BEAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20% AUM correction compresses base fees ~15% from $27.8B street; assumes tariff/market shock in H1 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bull-Case DCF Revenue — FY26E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF_REV_FY26_BULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH Bull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-end StockAnalysis estimate; assumes full Aladdin ACV + GIP/HPS ramp; https://stockanalysis.com/stocks/blk/forecast/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCK C — CONSENSUS vs. ASSUMPTION BRIDGE  (auto-calculated, do not edit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street Consensus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH Assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta ($MM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26E Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Above street: full Aladdin ACV + GIP fee ramp; consistent with 20-analyst SA avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26E Adj. EPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A — street only, no HH overlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used as reference in IS sheet; no DCF adjustment applied to EPS directly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOR LEGEND  |  BLUE = editable input (change when consensus updates)  |  BLACK = formula (auto-calculates, do not edit)  |  GREEN = cross-sheet reference from another tab</t>
+  </si>
+  <si>
     <t xml:space="preserve">BlackRock, Inc. (BLK)  |  Income Statement Summary</t>
   </si>
   <si>
@@ -204,6 +379,12 @@
     <t xml:space="preserve">Total Revenue</t>
   </si>
   <si>
+    <t xml:space="preserve">← Base-Case DCF Revenue Assumption (see Assumptions!D14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← Street FY26 Revenue Consensus</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Revenue Growth (YoY)</t>
   </si>
   <si>
@@ -246,7 +427,13 @@
     <t xml:space="preserve">GAAP Diluted EPS</t>
   </si>
   <si>
+    <t xml:space="preserve">← Street FY26 GAAP EPS Consensus (see Assumptions!D9)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adj. EPS (Non-GAAP, as reported)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← Street FY26 Adj. EPS Consensus (see Assumptions!D10)</t>
   </si>
   <si>
     <t xml:space="preserve">  YoY Adj. EPS Growth</t>
@@ -582,18 +769,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="0.00%;\(0.00%\);\-"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="171" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="172" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="173" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="174" formatCode="\$#,##0"/>
+    <numFmt numFmtId="175" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -702,8 +892,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -717,6 +908,28 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0D1B3E"/>
+      <name val="Courier New"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF006400"/>
       <name val="Calibri"/>
@@ -725,15 +938,22 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
+      <sz val="9"/>
       <color rgb="FF0D1B3E"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF006400"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="9"/>
+      <sz val="12"/>
       <color rgb="FF0D1B3E"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -769,15 +989,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,13 +1006,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF5EDD0"/>
+        <bgColor rgb="FFF9F3E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0D1B3E"/>
         <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F3E0"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -823,16 +1042,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5EDD0"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF9F3E0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -861,11 +1095,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="90">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -878,75 +1116,151 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -954,12 +1268,24 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -970,7 +1296,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -978,15 +1304,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -994,11 +1324,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1006,22 +1336,26 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1030,67 +1364,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1098,27 +1432,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1151,12 +1485,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF5EDD0"/>
+      <rgbColor rgb="FFF9F3E0"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1168,7 +1502,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFF5EDD0"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1374,501 +1708,509 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:M38"/>
+  <dimension ref="B1:M38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="1" width="15"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-    </row>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-    </row>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-    </row>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-    </row>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -1895,6 +2237,7 @@
     <mergeCell ref="B37:M38"/>
   </mergeCells>
   <hyperlinks>
+    <hyperlink ref="B28" location="'Assumptions'!B2" display="Assumptions"/>
     <hyperlink ref="B29" location="'Income Statement'!B2" display="Income Statement"/>
     <hyperlink ref="B30" location="'FCF Bridge'!B2" display="FCF Bridge"/>
     <hyperlink ref="B31" location="'WACC Calculator'!B2" display="WACC Calculator"/>
@@ -1916,625 +2259,1014 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J34"/>
+  <dimension ref="B2:H25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="21" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="C7" s="27" t="s">
         <v>56</v>
       </c>
+      <c r="D7" s="28" t="n">
+        <v>27774</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>31490</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>62.53</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>31490</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="28" t="n">
+        <v>23700</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>31100</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="34" t="n">
+        <f aca="false">Assumptions!D7</f>
+        <v>27774</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <f aca="false">Assumptions!D14</f>
+        <v>28500</v>
+      </c>
+      <c r="E21" s="35" t="n">
+        <f aca="false">D21-C21</f>
+        <v>726</v>
+      </c>
+      <c r="F21" s="36" t="n">
+        <f aca="false">(D21-C21)/C21</f>
+        <v>0.0261395549794772</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <f aca="false">Assumptions!D10</f>
+        <v>56.84</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B25:G25"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:L34"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+    </row>
+    <row r="4" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="23" t="n">
+      <c r="B7" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="43" t="n">
         <v>17873</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="43" t="n">
         <v>17859</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="43" t="n">
         <v>20407</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="43" t="n">
         <v>24219</v>
       </c>
-      <c r="G7" s="23" t="n">
-        <v>28480</v>
-      </c>
-      <c r="H7" s="23" t="n">
+      <c r="G7" s="44" t="n">
+        <f aca="false">Assumptions!D14</f>
+        <v>28500</v>
+      </c>
+      <c r="H7" s="43" t="n">
         <v>31490</v>
       </c>
-      <c r="I7" s="24" t="n">
+      <c r="I7" s="45" t="n">
         <f aca="false">(H7/C7)^(1/5)-1</f>
         <v>0.119940734386904</v>
       </c>
+      <c r="J7" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="K7" s="47" t="n">
+        <f aca="false">Assumptions!D7</f>
+        <v>27774</v>
+      </c>
+      <c r="L7" s="46" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="27" t="n">
+      <c r="B8" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="50" t="n">
         <f aca="false">(D7-C7)/C7</f>
         <v>-0.000783304425670005</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="50" t="n">
         <f aca="false">(E7-D7)/D7</f>
         <v>0.142673161991153</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="50" t="n">
         <f aca="false">(F7-E7)/E7</f>
         <v>0.186798647522909</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="50" t="n">
         <f aca="false">(G7-F7)/F7</f>
-        <v>0.175936248400017</v>
-      </c>
-      <c r="H8" s="27" t="n">
+        <v>0.176762046327264</v>
+      </c>
+      <c r="H8" s="50" t="n">
         <f aca="false">(H7-G7)/G7</f>
-        <v>0.105688202247191</v>
+        <v>0.104912280701754</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="23" t="n">
+      <c r="B10" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="43" t="n">
         <v>11394</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="43" t="n">
         <v>11513</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="43" t="n">
         <v>12729</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="43" t="n">
         <v>17184</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="43" t="n">
         <v>17525</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="43" t="n">
         <v>19524</v>
       </c>
-      <c r="I10" s="24" t="n">
+      <c r="I10" s="45" t="n">
         <f aca="false">(H10/C10)^(1/5)-1</f>
         <v>0.113726406113784</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="29" t="n">
+      <c r="B11" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="52" t="n">
         <f aca="false">C7-C10</f>
         <v>6479</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="52" t="n">
         <f aca="false">D7-D10</f>
         <v>6346</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="52" t="n">
         <f aca="false">E7-E10</f>
         <v>7678</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="52" t="n">
         <f aca="false">F7-F10</f>
         <v>7035</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="52" t="n">
         <f aca="false">G7-G10</f>
-        <v>10955</v>
-      </c>
-      <c r="H11" s="29" t="n">
+        <v>10975</v>
+      </c>
+      <c r="H11" s="52" t="n">
         <f aca="false">H7-H10</f>
         <v>11966</v>
       </c>
-      <c r="I11" s="24" t="n">
+      <c r="I11" s="45" t="n">
         <f aca="false">(H11/C11)^(1/5)-1</f>
         <v>0.130545911401076</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="24" t="n">
+      <c r="B12" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="45" t="n">
         <f aca="false">C11/C7</f>
         <v>0.362502098136854</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="45" t="n">
         <f aca="false">D11/D7</f>
         <v>0.355339044739347</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="45" t="n">
         <f aca="false">E11/E7</f>
         <v>0.376243445876415</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="45" t="n">
         <f aca="false">F11/F7</f>
         <v>0.290474420909204</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="45" t="n">
         <f aca="false">G11/G7</f>
-        <v>0.384655898876405</v>
-      </c>
-      <c r="H12" s="24" t="n">
+        <v>0.385087719298246</v>
+      </c>
+      <c r="H12" s="45" t="n">
         <f aca="false">H11/H7</f>
         <v>0.37999364877739</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
+      <c r="B14" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="23" t="n">
+      <c r="B15" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="43" t="n">
         <v>7685</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="43" t="n">
         <v>7514</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="43" t="n">
         <v>9075</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="43" t="n">
         <v>10681</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="43" t="n">
         <v>12551</v>
       </c>
-      <c r="H15" s="23" t="n">
+      <c r="H15" s="43" t="n">
         <v>13952</v>
       </c>
-      <c r="I15" s="24" t="n">
+      <c r="I15" s="45" t="n">
         <f aca="false">(H15/C15)^(1/5)-1</f>
         <v>0.126674640349674</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="30" t="n">
+      <c r="B16" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="53" t="n">
         <v>0.43</v>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="53" t="n">
         <v>0.421</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="53" t="n">
         <v>0.445</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="53" t="n">
         <v>0.441</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="45" t="n">
         <f aca="false">G15/G7</f>
-        <v>0.440695224719101</v>
-      </c>
-      <c r="H16" s="24" t="n">
+        <v>0.440385964912281</v>
+      </c>
+      <c r="H16" s="45" t="n">
         <f aca="false">H15/H7</f>
         <v>0.44306128929819</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="23" t="n">
+      <c r="B17" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="43" t="n">
         <v>418</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="43" t="n">
         <v>427</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="43" t="n">
         <v>529</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="43" t="n">
         <v>750</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="43" t="n">
         <v>900</v>
       </c>
-      <c r="H17" s="23" t="n">
+      <c r="H17" s="43" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="29" t="n">
+      <c r="B18" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="52" t="n">
         <f aca="false">C15+C17</f>
         <v>8103</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="52" t="n">
         <f aca="false">D15+D17</f>
         <v>7941</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="52" t="n">
         <f aca="false">E15+E17</f>
         <v>9604</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="52" t="n">
         <f aca="false">F15+F17</f>
         <v>11431</v>
       </c>
-      <c r="G18" s="29" t="n">
+      <c r="G18" s="52" t="n">
         <f aca="false">G15+G17</f>
         <v>13451</v>
       </c>
-      <c r="H18" s="29" t="n">
+      <c r="H18" s="52" t="n">
         <f aca="false">H15+H17</f>
         <v>14952</v>
       </c>
-      <c r="I18" s="24" t="n">
+      <c r="I18" s="45" t="n">
         <f aca="false">(H18/C18)^(1/5)-1</f>
         <v>0.130344147125297</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="24" t="n">
+      <c r="B19" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="45" t="n">
         <f aca="false">C18/C7</f>
         <v>0.453365411514575</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="45" t="n">
         <f aca="false">D18/D7</f>
         <v>0.444649756425332</v>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="45" t="n">
         <f aca="false">E18/E7</f>
         <v>0.470622825501054</v>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="45" t="n">
         <f aca="false">F18/F7</f>
         <v>0.471984805318139</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="45" t="n">
         <f aca="false">G18/G7</f>
-        <v>0.472296348314607</v>
-      </c>
-      <c r="H19" s="24" t="n">
+        <v>0.471964912280702</v>
+      </c>
+      <c r="H19" s="45" t="n">
         <f aca="false">H18/H7</f>
         <v>0.474817402349952</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
+      <c r="B21" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="31" t="n">
+      <c r="B22" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="54" t="n">
         <v>33.97</v>
       </c>
-      <c r="D22" s="31" t="n">
+      <c r="D22" s="54" t="n">
         <v>36.51</v>
       </c>
-      <c r="E22" s="31" t="n">
+      <c r="E22" s="54" t="n">
         <v>42.01</v>
       </c>
-      <c r="F22" s="31" t="n">
+      <c r="F22" s="54" t="n">
         <v>35.31</v>
       </c>
-      <c r="G22" s="31" t="n">
+      <c r="G22" s="55" t="n">
+        <f aca="false">Assumptions!D9</f>
         <v>54.95</v>
       </c>
-      <c r="H22" s="31" t="n">
+      <c r="H22" s="54" t="n">
         <v>62.53</v>
       </c>
-      <c r="I22" s="24" t="n">
+      <c r="I22" s="45" t="n">
         <f aca="false">(H22/C22)^(1/5)-1</f>
         <v>0.129792211154373</v>
       </c>
+      <c r="J22" s="46" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="31" t="n">
+      <c r="B23" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="54" t="n">
         <v>39.18</v>
       </c>
-      <c r="D23" s="31" t="n">
+      <c r="D23" s="54" t="n">
         <v>41.52</v>
       </c>
-      <c r="E23" s="31" t="n">
+      <c r="E23" s="54" t="n">
         <v>43.61</v>
       </c>
-      <c r="F23" s="31" t="n">
+      <c r="F23" s="54" t="n">
         <v>48.09</v>
       </c>
-      <c r="G23" s="31" t="n">
-        <v>54.44</v>
-      </c>
-      <c r="H23" s="31" t="n">
+      <c r="G23" s="55" t="n">
+        <f aca="false">Assumptions!D10</f>
+        <v>56.84</v>
+      </c>
+      <c r="H23" s="54" t="n">
         <v>61.8</v>
       </c>
-      <c r="I23" s="24" t="n">
+      <c r="I23" s="45" t="n">
         <f aca="false">(H23/C23)^(1/5)-1</f>
         <v>0.0954304492810594</v>
       </c>
+      <c r="J23" s="46" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="27" t="n">
+      <c r="B24" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="50" t="n">
         <f aca="false">(D23-C23)/C23</f>
         <v>0.0597243491577336</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="50" t="n">
         <f aca="false">(E23-D23)/D23</f>
         <v>0.0503371868978805</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="50" t="n">
         <f aca="false">(F23-E23)/E23</f>
         <v>0.102728731942215</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="50" t="n">
         <f aca="false">(G23-F23)/F23</f>
-        <v>0.132044084009149</v>
-      </c>
-      <c r="H24" s="27" t="n">
+        <v>0.181950509461427</v>
+      </c>
+      <c r="H24" s="50" t="n">
         <f aca="false">(H23-G23)/G23</f>
-        <v>0.135194709772226</v>
+        <v>0.0872624912033778</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="33" t="n">
+      <c r="B25" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" s="57" t="n">
         <v>152</v>
       </c>
-      <c r="D25" s="33" t="n">
+      <c r="D25" s="57" t="n">
         <v>151</v>
       </c>
-      <c r="E25" s="33" t="n">
+      <c r="E25" s="57" t="n">
         <v>152</v>
       </c>
-      <c r="F25" s="33" t="n">
+      <c r="F25" s="57" t="n">
         <v>157</v>
       </c>
-      <c r="G25" s="33" t="n">
+      <c r="G25" s="57" t="n">
         <v>158</v>
       </c>
-      <c r="H25" s="33" t="n">
+      <c r="H25" s="57" t="n">
         <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="31" t="n">
+      <c r="B26" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="54" t="n">
         <v>16.52</v>
       </c>
-      <c r="D26" s="31" t="n">
+      <c r="D26" s="54" t="n">
         <v>19.52</v>
       </c>
-      <c r="E26" s="31" t="n">
+      <c r="E26" s="54" t="n">
         <v>20.4</v>
       </c>
-      <c r="F26" s="31" t="n">
+      <c r="F26" s="54" t="n">
         <v>20.84</v>
       </c>
-      <c r="G26" s="31" t="n">
+      <c r="G26" s="54" t="n">
         <v>22.92</v>
       </c>
-      <c r="H26" s="31" t="n">
+      <c r="H26" s="54" t="n">
         <v>25.21</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
+      <c r="B28" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="34" t="n">
+      <c r="B29" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="58" t="n">
         <v>8.59</v>
       </c>
-      <c r="D29" s="34" t="n">
+      <c r="D29" s="58" t="n">
         <v>9.09</v>
       </c>
-      <c r="E29" s="34" t="n">
+      <c r="E29" s="58" t="n">
         <v>11.55</v>
       </c>
-      <c r="F29" s="34" t="n">
+      <c r="F29" s="58" t="n">
         <v>14.04</v>
       </c>
-      <c r="G29" s="34" t="n">
+      <c r="G29" s="58" t="n">
         <v>15.5</v>
       </c>
-      <c r="H29" s="34" t="n">
+      <c r="H29" s="58" t="n">
         <v>17.05</v>
       </c>
-      <c r="I29" s="24" t="n">
+      <c r="I29" s="45" t="n">
         <f aca="false">(H29/C29)^(1/5)-1</f>
         <v>0.14695464323997</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="27" t="n">
+      <c r="B30" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="50" t="n">
         <f aca="false">(D29-C29)/C29</f>
         <v>0.0582072176949942</v>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="50" t="n">
         <f aca="false">(E29-D29)/D29</f>
         <v>0.270627062706271</v>
       </c>
-      <c r="F30" s="27" t="n">
+      <c r="F30" s="50" t="n">
         <f aca="false">(F29-E29)/E29</f>
         <v>0.215584415584415</v>
       </c>
-      <c r="G30" s="27" t="n">
+      <c r="G30" s="50" t="n">
         <f aca="false">(G29-F29)/F29</f>
         <v>0.103988603988604</v>
       </c>
-      <c r="H30" s="27" t="n">
+      <c r="H30" s="50" t="n">
         <f aca="false">(H29-G29)/G29</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
+      <c r="B33" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="59"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2557,7 +3289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2565,529 +3297,529 @@
   <dimension ref="B2:J29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
+      <c r="B2" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
     </row>
     <row r="4" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>56</v>
+      <c r="B5" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="n">
+      <c r="B7" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="43" t="n">
         <v>8103</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="43" t="n">
         <v>7941</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="43" t="n">
         <v>9604</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="43" t="n">
         <v>11431</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="43" t="n">
         <v>13451</v>
       </c>
-      <c r="H7" s="23" t="n">
+      <c r="H7" s="43" t="n">
         <v>14952</v>
       </c>
-      <c r="I7" s="24" t="n">
+      <c r="I7" s="45" t="n">
         <f aca="false">(H7/C7)^(1/5)-1</f>
         <v>0.130344147125297</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="23" t="n">
+      <c r="B8" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="43" t="n">
         <v>-418</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="43" t="n">
         <v>-427</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="43" t="n">
         <v>-529</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="43" t="n">
         <v>-750</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="43" t="n">
         <v>-900</v>
       </c>
-      <c r="H8" s="23" t="n">
+      <c r="H8" s="43" t="n">
         <v>-1000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="36" t="n">
+      <c r="B9" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="60" t="n">
         <f aca="false">C7+C8</f>
         <v>7685</v>
       </c>
-      <c r="D9" s="36" t="n">
+      <c r="D9" s="60" t="n">
         <f aca="false">D7+D8</f>
         <v>7514</v>
       </c>
-      <c r="E9" s="36" t="n">
+      <c r="E9" s="60" t="n">
         <f aca="false">E7+E8</f>
         <v>9075</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="60" t="n">
         <f aca="false">F7+F8</f>
         <v>10681</v>
       </c>
-      <c r="G9" s="36" t="n">
+      <c r="G9" s="60" t="n">
         <f aca="false">G7+G8</f>
         <v>12551</v>
       </c>
-      <c r="H9" s="36" t="n">
+      <c r="H9" s="60" t="n">
         <f aca="false">H7+H8</f>
         <v>13952</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="30" t="n">
+      <c r="B10" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="53" t="n">
         <v>0.206</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="53" t="n">
         <v>0.207</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="53" t="n">
         <v>0.215</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="53" t="n">
         <v>0.214</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="53" t="n">
         <v>0.215</v>
       </c>
-      <c r="H10" s="30" t="n">
+      <c r="H10" s="53" t="n">
         <v>0.215</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="29" t="n">
+      <c r="B11" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="52" t="n">
         <f aca="false">C9*(1-C10)</f>
         <v>6101.89</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="52" t="n">
         <f aca="false">D9*(1-D10)</f>
         <v>5958.602</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="52" t="n">
         <f aca="false">E9*(1-E10)</f>
         <v>7123.875</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="52" t="n">
         <f aca="false">F9*(1-F10)</f>
         <v>8395.266</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="52" t="n">
         <f aca="false">G9*(1-G10)</f>
         <v>9852.535</v>
       </c>
-      <c r="H11" s="29" t="n">
+      <c r="H11" s="52" t="n">
         <f aca="false">H9*(1-H10)</f>
         <v>10952.32</v>
       </c>
-      <c r="I11" s="24" t="n">
+      <c r="I11" s="45" t="n">
         <f aca="false">(H11/C11)^(1/5)-1</f>
         <v>0.124108806072756</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
+      <c r="B13" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="37" t="n">
+      <c r="B14" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="61" t="n">
         <f aca="false">C11</f>
         <v>6101.89</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="61" t="n">
         <f aca="false">D11</f>
         <v>5958.602</v>
       </c>
-      <c r="E14" s="37" t="n">
+      <c r="E14" s="61" t="n">
         <f aca="false">E11</f>
         <v>7123.875</v>
       </c>
-      <c r="F14" s="37" t="n">
+      <c r="F14" s="61" t="n">
         <f aca="false">F11</f>
         <v>8395.266</v>
       </c>
-      <c r="G14" s="37" t="n">
+      <c r="G14" s="61" t="n">
         <f aca="false">G11</f>
         <v>9852.535</v>
       </c>
-      <c r="H14" s="37" t="n">
+      <c r="H14" s="61" t="n">
         <f aca="false">H11</f>
         <v>10952.32</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="23" t="n">
+      <c r="B15" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="43" t="n">
         <v>418</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="43" t="n">
         <v>427</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="43" t="n">
         <v>529</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="43" t="n">
         <v>750</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="43" t="n">
         <v>900</v>
       </c>
-      <c r="H15" s="23" t="n">
+      <c r="H15" s="43" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="23" t="n">
+      <c r="B16" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="43" t="n">
         <v>708</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="43" t="n">
         <v>630</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="43" t="n">
         <v>753</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="43" t="n">
         <v>850</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G16" s="43" t="n">
         <v>950</v>
       </c>
-      <c r="H16" s="23" t="n">
+      <c r="H16" s="43" t="n">
         <v>1050</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="23" t="n">
+      <c r="B17" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="43" t="n">
         <v>570</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="43" t="n">
         <v>321</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="43" t="n">
         <v>-515</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="43" t="n">
         <v>-300</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="43" t="n">
         <v>-200</v>
       </c>
-      <c r="H17" s="23" t="n">
+      <c r="H17" s="43" t="n">
         <v>-150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="23" t="n">
+      <c r="B18" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="C18" s="43" t="n">
         <v>-533</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="43" t="n">
         <v>-344</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="43" t="n">
         <v>-255</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="43" t="n">
         <v>-375</v>
       </c>
-      <c r="G18" s="23" t="n">
+      <c r="G18" s="43" t="n">
         <v>-450</v>
       </c>
-      <c r="H18" s="23" t="n">
+      <c r="H18" s="43" t="n">
         <v>-500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="29" t="n">
+      <c r="B19" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="52" t="n">
         <f aca="false">C14+C15+C16+C17+C18</f>
         <v>7264.89</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="52" t="n">
         <f aca="false">D14+D15+D16+D17+D18</f>
         <v>6992.602</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="52" t="n">
         <f aca="false">E14+E15+E16+E17+E18</f>
         <v>7635.875</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="52" t="n">
         <f aca="false">F14+F15+F16+F17+F18</f>
         <v>9320.266</v>
       </c>
-      <c r="G19" s="29" t="n">
+      <c r="G19" s="52" t="n">
         <f aca="false">G14+G15+G16+G17+G18</f>
         <v>11052.535</v>
       </c>
-      <c r="H19" s="29" t="n">
+      <c r="H19" s="52" t="n">
         <f aca="false">H14+H15+H16+H17+H18</f>
         <v>12352.32</v>
       </c>
-      <c r="I19" s="24" t="n">
+      <c r="I19" s="45" t="n">
         <f aca="false">(H19/C19)^(1/5)-1</f>
         <v>0.111997723676154</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="27" t="n">
+      <c r="B20" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="50" t="n">
         <f aca="false">C19/17873</f>
         <v>0.40647289207184</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="50" t="n">
         <f aca="false">D19/17859</f>
         <v>0.391544991320903</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="50" t="n">
         <f aca="false">E19/20407</f>
         <v>0.374179203214583</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="50" t="n">
         <f aca="false">F19/24219</f>
         <v>0.384832817209629</v>
       </c>
-      <c r="G20" s="27" t="n">
-        <f aca="false">G19/28480</f>
-        <v>0.388080582865169</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <f aca="false">H19/31490</f>
+      <c r="G20" s="62" t="n">
+        <f aca="false">G19/Assumptions!D14</f>
+        <v>0.387808245614035</v>
+      </c>
+      <c r="H20" s="62" t="n">
+        <f aca="false">H19/Assumptions!D8</f>
         <v>0.392261670371547</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
+      <c r="B22" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="23" t="n">
+      <c r="B23" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="43" t="n">
         <v>-168</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="43" t="n">
         <v>-232</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="43" t="n">
         <v>-422</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F23" s="43" t="n">
         <v>-483</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="43" t="n">
         <v>-487</v>
       </c>
-      <c r="H23" s="23" t="n">
+      <c r="H23" s="43" t="n">
         <v>-487</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="23" t="n">
+      <c r="B24" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F24" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G24" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="23" t="n">
+      <c r="H24" s="43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="29" t="n">
+      <c r="B25" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="52" t="n">
         <f aca="false">C19+C23+C24</f>
         <v>7096.89</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="52" t="n">
         <f aca="false">D19+D23+D24</f>
         <v>6760.602</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="52" t="n">
         <f aca="false">E19+E23+E24</f>
         <v>7213.875</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="52" t="n">
         <f aca="false">F19+F23+F24</f>
         <v>8837.266</v>
       </c>
-      <c r="G25" s="29" t="n">
+      <c r="G25" s="52" t="n">
         <f aca="false">G19+G23+G24</f>
         <v>10565.535</v>
       </c>
-      <c r="H25" s="29" t="n">
+      <c r="H25" s="52" t="n">
         <f aca="false">H19+H23+H24</f>
         <v>11865.32</v>
       </c>
-      <c r="I25" s="24" t="n">
+      <c r="I25" s="45" t="n">
         <f aca="false">(H25/C25)^(1/5)-1</f>
         <v>0.108261576058217</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
+      <c r="B28" s="59" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3108,7 +3840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3116,346 +3848,346 @@
   <dimension ref="B2:G29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B2" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>108</v>
+      <c r="B5" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="30" t="n">
+      <c r="B7" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" s="53" t="n">
         <v>0.043</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="53" t="n">
         <v>0.043</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="53" t="n">
         <v>0.043</v>
       </c>
-      <c r="F7" s="40" t="s">
-        <v>111</v>
+      <c r="F7" s="65" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="30" t="n">
+      <c r="B8" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="53" t="n">
         <v>1.2</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="53" t="n">
         <v>1.36</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="40" t="s">
-        <v>113</v>
+      <c r="F8" s="65" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C9" s="30" t="n">
+      <c r="B9" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="53" t="n">
         <v>0.055</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="53" t="n">
         <v>0.06</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="53" t="n">
         <v>0.05</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>115</v>
+      <c r="F9" s="65" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="42" t="n">
+      <c r="B10" s="66" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="67" t="n">
         <f aca="false">C7+C8*C9</f>
         <v>0.109</v>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D10" s="67" t="n">
         <f aca="false">D7+D8*D9</f>
         <v>0.1246</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="67" t="n">
         <f aca="false">E7+E8*E9</f>
         <v>0.093</v>
       </c>
-      <c r="F10" s="43" t="s">
-        <v>117</v>
+      <c r="F10" s="68" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="B12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="30" t="n">
+      <c r="B13" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="53" t="n">
         <v>0.0463</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="53" t="n">
         <v>0.05</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="53" t="n">
         <v>0.043</v>
       </c>
-      <c r="F13" s="40" t="s">
-        <v>120</v>
+      <c r="F13" s="65" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="30" t="n">
+      <c r="B14" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" s="53" t="n">
         <v>0.214</v>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="53" t="n">
         <v>0.214</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="53" t="n">
         <v>0.214</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>122</v>
+      <c r="F14" s="65" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="42" t="n">
+      <c r="B15" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" s="67" t="n">
         <f aca="false">C13*(1-C14)</f>
         <v>0.0363918</v>
       </c>
-      <c r="D15" s="42" t="n">
+      <c r="D15" s="67" t="n">
         <f aca="false">D13*(1-D14)</f>
         <v>0.0393</v>
       </c>
-      <c r="E15" s="42" t="n">
+      <c r="E15" s="67" t="n">
         <f aca="false">E13*(1-E14)</f>
         <v>0.033798</v>
       </c>
-      <c r="F15" s="43" t="s">
-        <v>124</v>
+      <c r="F15" s="68" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="B17" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C18" s="23" t="n">
+      <c r="B18" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="43" t="n">
         <v>155000</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="43" t="n">
         <v>140000</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="43" t="n">
         <v>175000</v>
       </c>
-      <c r="F18" s="40" t="s">
-        <v>127</v>
+      <c r="F18" s="65" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C19" s="23" t="n">
+      <c r="B19" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="43" t="n">
         <v>12800</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="43" t="n">
         <v>12800</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="43" t="n">
         <v>12800</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>129</v>
+      <c r="F19" s="65" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" s="36" t="n">
+      <c r="B20" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" s="60" t="n">
         <f aca="false">C18+C19</f>
         <v>167800</v>
       </c>
-      <c r="D20" s="36" t="n">
+      <c r="D20" s="60" t="n">
         <f aca="false">D18+D19</f>
         <v>152800</v>
       </c>
-      <c r="E20" s="36" t="n">
+      <c r="E20" s="60" t="n">
         <f aca="false">E18+E19</f>
         <v>187800</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="24" t="n">
+      <c r="B21" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="45" t="n">
         <f aca="false">C18/C20</f>
         <v>0.923718712753278</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="45" t="n">
         <f aca="false">D18/D20</f>
         <v>0.916230366492147</v>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="45" t="n">
         <f aca="false">E18/E20</f>
         <v>0.931842385516507</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="24" t="n">
+      <c r="B22" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="45" t="n">
         <f aca="false">1-C21</f>
         <v>0.0762812872467223</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="45" t="n">
         <f aca="false">1-D21</f>
         <v>0.0837696335078534</v>
       </c>
-      <c r="E22" s="24" t="n">
+      <c r="E22" s="45" t="n">
         <f aca="false">1-E21</f>
         <v>0.0681576144834931</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="B24" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="45" t="n">
+      <c r="C25" s="70" t="n">
         <f aca="false">C10*C21+C15*C22</f>
         <v>0.103461353039333</v>
       </c>
-      <c r="D25" s="45" t="n">
+      <c r="D25" s="70" t="n">
         <f aca="false">D10*D21+D15*D22</f>
         <v>0.11745445026178</v>
       </c>
-      <c r="E25" s="45" t="n">
+      <c r="E25" s="70" t="n">
         <f aca="false">E10*E21+E15*E22</f>
         <v>0.0889649329073483</v>
       </c>
-      <c r="F25" s="46" t="s">
-        <v>134</v>
+      <c r="F25" s="71" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
+      <c r="B27" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="59"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3477,7 +4209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3485,507 +4217,507 @@
   <dimension ref="B2:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B2" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>139</v>
+      <c r="B5" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="47" t="n">
+      <c r="B7" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="72" t="n">
         <v>0.11</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="72" t="n">
         <v>0.095</v>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="72" t="n">
         <v>0.08</v>
       </c>
-      <c r="F7" s="43" t="s">
-        <v>142</v>
+      <c r="F7" s="68" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="47" t="n">
+      <c r="B8" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="72" t="n">
         <v>0.02</v>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="72" t="n">
         <v>0.025</v>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="72" t="n">
         <v>0.0325</v>
       </c>
-      <c r="F8" s="43" t="s">
-        <v>144</v>
+      <c r="F8" s="68" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
+      <c r="B10" s="73" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="23" t="n">
+      <c r="B11" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="43" t="n">
         <v>3800</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="43" t="n">
         <v>5200</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="43" t="n">
         <v>6800</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="23" t="n">
+      <c r="B12" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" s="43" t="n">
         <v>4100</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="43" t="n">
         <v>5800</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="43" t="n">
         <v>7800</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="23" t="n">
+      <c r="B13" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" s="43" t="n">
         <v>4300</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="43" t="n">
         <v>6200</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="43" t="n">
         <v>8500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="23" t="n">
+      <c r="B14" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" s="43" t="n">
         <v>4500</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="43" t="n">
         <v>6600</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="43" t="n">
         <v>9200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
+      <c r="B15" s="73" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="36" t="n">
+      <c r="B16" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="60" t="n">
         <f aca="false">C11/((1+C7)^1)</f>
         <v>3423.42342342342</v>
       </c>
-      <c r="D16" s="36" t="n">
+      <c r="D16" s="60" t="n">
         <f aca="false">D11/((1+D7)^1)</f>
         <v>4748.85844748859</v>
       </c>
-      <c r="E16" s="36" t="n">
+      <c r="E16" s="60" t="n">
         <f aca="false">E11/((1+E7)^1)</f>
         <v>6296.2962962963</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" s="36" t="n">
+      <c r="B17" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="60" t="n">
         <f aca="false">C12/((1+C7)^2)</f>
         <v>3327.65197630062</v>
       </c>
-      <c r="D17" s="36" t="n">
+      <c r="D17" s="60" t="n">
         <f aca="false">D12/((1+D7)^2)</f>
         <v>4837.26361001647</v>
       </c>
-      <c r="E17" s="36" t="n">
+      <c r="E17" s="60" t="n">
         <f aca="false">E12/((1+E7)^2)</f>
         <v>6687.24279835391</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="C18" s="36" t="n">
+      <c r="B18" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="60" t="n">
         <f aca="false">C13/((1+C7)^3)</f>
         <v>3144.12293959409</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="60" t="n">
         <f aca="false">D13/((1+D7)^3)</f>
         <v>4722.25387846042</v>
       </c>
-      <c r="E18" s="36" t="n">
+      <c r="E18" s="60" t="n">
         <f aca="false">E13/((1+E7)^3)</f>
         <v>6747.57404867144</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="36" t="n">
+      <c r="B19" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" s="60" t="n">
         <f aca="false">C14/((1+C7)^4)</f>
         <v>2964.2893836525</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="60" t="n">
         <f aca="false">D14/((1+D7)^4)</f>
         <v>4590.79033699201</v>
       </c>
-      <c r="E19" s="36" t="n">
+      <c r="E19" s="60" t="n">
         <f aca="false">E14/((1+E7)^4)</f>
         <v>6762.27464572737</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="29" t="n">
+      <c r="B20" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="C20" s="52" t="n">
         <f aca="false">C16+C17+C18+C19</f>
         <v>12859.4877229706</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="52" t="n">
         <f aca="false">D16+D17+D18+D19</f>
         <v>18899.1662729575</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="52" t="n">
         <f aca="false">E16+E17+E18+E19</f>
         <v>26493.387789049</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="B22" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="C23" s="36" t="n">
+      <c r="B23" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="C23" s="60" t="n">
         <f aca="false">C14</f>
         <v>4500</v>
       </c>
-      <c r="D23" s="36" t="n">
+      <c r="D23" s="60" t="n">
         <f aca="false">D14</f>
         <v>6600</v>
       </c>
-      <c r="E23" s="36" t="n">
+      <c r="E23" s="60" t="n">
         <f aca="false">E14</f>
         <v>9200</v>
       </c>
-      <c r="F23" s="43" t="s">
-        <v>158</v>
+      <c r="F23" s="68" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C24" s="29" t="n">
+      <c r="B24" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="52" t="n">
         <f aca="false">C23*(1+C8)/(C7-C8)</f>
         <v>51000</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="52" t="n">
         <f aca="false">D23*(1+D8)/(D7-D8)</f>
         <v>96642.8571428571</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="52" t="n">
         <f aca="false">E23*(1+E8)/(E7-E8)</f>
         <v>199978.947368421</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="C25" s="36" t="n">
+      <c r="B25" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" s="60" t="n">
         <f aca="false">C24/((1+C7)^4)</f>
         <v>33595.279681395</v>
       </c>
-      <c r="D25" s="36" t="n">
+      <c r="D25" s="60" t="n">
         <f aca="false">D24/((1+D7)^4)</f>
         <v>67222.287077383</v>
       </c>
-      <c r="E25" s="36" t="n">
+      <c r="E25" s="60" t="n">
         <f aca="false">E24/((1+E7)^4)</f>
         <v>146990.4962466</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="C26" s="27" t="n">
+      <c r="B26" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" s="50" t="n">
         <f aca="false">C25/C29</f>
         <v>0.723182604466939</v>
       </c>
-      <c r="D26" s="27" t="n">
+      <c r="D26" s="50" t="n">
         <f aca="false">D25/D29</f>
         <v>0.780552167459645</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="50" t="n">
         <f aca="false">E25/E29</f>
         <v>0.847286173373863</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="B28" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" s="29" t="n">
+      <c r="B29" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29" s="52" t="n">
         <f aca="false">C20+C25</f>
         <v>46454.7674043656</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="52" t="n">
         <f aca="false">D20+D25</f>
         <v>86121.4533503405</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="52" t="n">
         <f aca="false">E20+E25</f>
         <v>173483.884035649</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="C30" s="23" t="n">
+      <c r="B30" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="43" t="n">
         <v>1300</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="43" t="n">
         <v>1300</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="43" t="n">
         <v>1300</v>
       </c>
-      <c r="F30" s="43" t="s">
-        <v>165</v>
+      <c r="F30" s="68" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C31" s="29" t="n">
+      <c r="B31" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" s="52" t="n">
         <f aca="false">C29-C30</f>
         <v>45154.7674043656</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="52" t="n">
         <f aca="false">D29-D30</f>
         <v>84821.4533503405</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="52" t="n">
         <f aca="false">E29-E30</f>
         <v>172183.884035649</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="C32" s="33" t="n">
+      <c r="B32" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="C32" s="57" t="n">
         <v>159</v>
       </c>
-      <c r="D32" s="33" t="n">
+      <c r="D32" s="57" t="n">
         <v>159</v>
       </c>
-      <c r="E32" s="33" t="n">
+      <c r="E32" s="57" t="n">
         <v>159</v>
       </c>
-      <c r="F32" s="43" t="s">
-        <v>168</v>
+      <c r="F32" s="68" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="C33" s="49" t="n">
+      <c r="B33" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="C33" s="74" t="n">
         <f aca="false">C31/C32</f>
         <v>283.992247826199</v>
       </c>
-      <c r="D33" s="50" t="n">
+      <c r="D33" s="75" t="n">
         <f aca="false">D31/D32</f>
         <v>533.468260065035</v>
       </c>
-      <c r="E33" s="51" t="n">
+      <c r="E33" s="76" t="n">
         <f aca="false">E31/E32</f>
         <v>1082.91750965817</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="C34" s="52" t="n">
+      <c r="B34" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="C34" s="77" t="n">
         <v>958</v>
       </c>
-      <c r="D34" s="52" t="n">
+      <c r="D34" s="77" t="n">
         <v>958</v>
       </c>
-      <c r="E34" s="52" t="n">
+      <c r="E34" s="77" t="n">
         <v>958</v>
       </c>
-      <c r="F34" s="43" t="s">
-        <v>171</v>
+      <c r="F34" s="68" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="C35" s="24" t="n">
+      <c r="B35" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" s="45" t="n">
         <f aca="false">(C33-C34)/C34</f>
         <v>-0.703557152582256</v>
       </c>
-      <c r="D35" s="24" t="n">
+      <c r="D35" s="45" t="n">
         <f aca="false">(D33-D34)/D34</f>
         <v>-0.443143778637751</v>
       </c>
-      <c r="E35" s="24" t="n">
+      <c r="E35" s="45" t="n">
         <f aca="false">(E33-E34)/E34</f>
         <v>0.130394060185982</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="53" t="s">
-        <v>173</v>
-      </c>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="53"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
+      <c r="B37" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="C37" s="78"/>
+      <c r="D37" s="78"/>
+      <c r="E37" s="78"/>
+      <c r="F37" s="78"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="78"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="78"/>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="35"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
+      <c r="B40" s="59" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4009,7 +4741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4017,816 +4749,816 @@
   <dimension ref="B2:O47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
+      <c r="B2" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
     </row>
     <row r="4" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="54" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
+      <c r="B6" s="79" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="56" t="n">
+      <c r="B7" s="80" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="81" t="n">
         <v>0.015</v>
       </c>
-      <c r="D7" s="56" t="n">
+      <c r="D7" s="81" t="n">
         <v>0.02</v>
       </c>
-      <c r="E7" s="56" t="n">
+      <c r="E7" s="81" t="n">
         <v>0.025</v>
       </c>
-      <c r="F7" s="56" t="n">
+      <c r="F7" s="81" t="n">
         <v>0.03</v>
       </c>
-      <c r="G7" s="56" t="n">
+      <c r="G7" s="81" t="n">
         <v>0.035</v>
       </c>
-      <c r="H7" s="56" t="n">
+      <c r="H7" s="81" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="81" t="n">
         <v>0.075</v>
       </c>
-      <c r="C8" s="57" t="n">
+      <c r="C8" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.075)^1)+4100/((1+0.075)^2)+4300/((1+0.075)^3)+4500/((1+0.075)^4)+(4500*(1+0.015)/(0.075-0.015))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>437.837236434939</v>
       </c>
-      <c r="D8" s="57" t="n">
+      <c r="D8" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.075)^1)+4100/((1+0.075)^2)+4300/((1+0.075)^3)+4500/((1+0.075)^4)+(4500*(1+0.02)/(0.075-0.02))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>472.355271148044</v>
       </c>
-      <c r="E8" s="57" t="n">
+      <c r="E8" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.075)^1)+4100/((1+0.075)^2)+4300/((1+0.075)^3)+4500/((1+0.075)^4)+(4500*(1+0.025)/(0.075-0.025))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>513.77691280377</v>
       </c>
-      <c r="F8" s="57" t="n">
+      <c r="F8" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.075)^1)+4100/((1+0.075)^2)+4300/((1+0.075)^3)+4500/((1+0.075)^4)+(4500*(1+0.03)/(0.075-0.03))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>564.403363716323</v>
       </c>
-      <c r="G8" s="57" t="n">
+      <c r="G8" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.075)^1)+4100/((1+0.075)^2)+4300/((1+0.075)^3)+4500/((1+0.075)^4)+(4500*(1+0.035)/(0.075-0.035))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>627.686427357015</v>
       </c>
-      <c r="H8" s="57" t="n">
+      <c r="H8" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.075)^1)+4100/((1+0.075)^2)+4300/((1+0.075)^3)+4500/((1+0.075)^4)+(4500*(1+0.04)/(0.075-0.04))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>709.05036632362</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="81" t="n">
         <v>0.085</v>
       </c>
-      <c r="C9" s="57" t="n">
+      <c r="C9" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.085)^1)+4100/((1+0.085)^2)+4300/((1+0.085)^3)+4500/((1+0.085)^4)+(4500*(1+0.015)/(0.085-0.015))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>373.467811158971</v>
       </c>
-      <c r="D9" s="57" t="n">
+      <c r="D9" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.085)^1)+4100/((1+0.085)^2)+4300/((1+0.085)^3)+4500/((1+0.085)^4)+(4500*(1+0.02)/(0.085-0.02))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>397.817015961917</v>
       </c>
-      <c r="E9" s="57" t="n">
+      <c r="E9" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.085)^1)+4100/((1+0.085)^2)+4300/((1+0.085)^3)+4500/((1+0.085)^4)+(4500*(1+0.025)/(0.085-0.025))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>426.224421565355</v>
       </c>
-      <c r="F9" s="57" t="n">
+      <c r="F9" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.085)^1)+4100/((1+0.085)^2)+4300/((1+0.085)^3)+4500/((1+0.085)^4)+(4500*(1+0.03)/(0.085-0.03))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>459.79681000578</v>
       </c>
-      <c r="G9" s="57" t="n">
+      <c r="G9" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.085)^1)+4100/((1+0.085)^2)+4300/((1+0.085)^3)+4500/((1+0.085)^4)+(4500*(1+0.035)/(0.085-0.035))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>500.083676134291</v>
       </c>
-      <c r="H9" s="57" t="n">
+      <c r="H9" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.085)^1)+4100/((1+0.085)^2)+4300/((1+0.085)^3)+4500/((1+0.085)^4)+(4500*(1+0.04)/(0.085-0.04))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>549.323179180249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="81" t="n">
         <v>0.095</v>
       </c>
-      <c r="C10" s="57" t="n">
+      <c r="C10" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.095)^1)+4100/((1+0.095)^2)+4300/((1+0.095)^3)+4500/((1+0.095)^4)+(4500*(1+0.015)/(0.095-0.015))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>325.206951575661</v>
       </c>
-      <c r="D10" s="57" t="n">
+      <c r="D10" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.095)^1)+4100/((1+0.095)^2)+4300/((1+0.095)^3)+4500/((1+0.095)^4)+(4500*(1+0.02)/(0.095-0.02))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>343.170485805958</v>
       </c>
-      <c r="E10" s="57" t="n">
+      <c r="E10" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.095)^1)+4100/((1+0.095)^2)+4300/((1+0.095)^3)+4500/((1+0.095)^4)+(4500*(1+0.025)/(0.095-0.025))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>363.700239212011</v>
       </c>
-      <c r="F10" s="57" t="n">
+      <c r="F10" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.095)^1)+4100/((1+0.095)^2)+4300/((1+0.095)^3)+4500/((1+0.095)^4)+(4500*(1+0.03)/(0.095-0.03))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>387.388416218996</v>
       </c>
-      <c r="G10" s="57" t="n">
+      <c r="G10" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.095)^1)+4100/((1+0.095)^2)+4300/((1+0.095)^3)+4500/((1+0.095)^4)+(4500*(1+0.035)/(0.095-0.035))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>415.024622727145</v>
       </c>
-      <c r="H10" s="57" t="n">
+      <c r="H10" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.095)^1)+4100/((1+0.095)^2)+4300/((1+0.095)^3)+4500/((1+0.095)^4)+(4500*(1+0.04)/(0.095-0.04))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>447.685594054957</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="56" t="n">
+      <c r="B11" s="81" t="n">
         <v>0.1</v>
       </c>
-      <c r="C11" s="57" t="n">
+      <c r="C11" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.1)^1)+4100/((1+0.1)^2)+4300/((1+0.1)^3)+4500/((1+0.1)^4)+(4500*(1+0.015)/(0.1-0.015))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>305.340366729457</v>
       </c>
-      <c r="D11" s="57" t="n">
+      <c r="D11" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.1)^1)+4100/((1+0.1)^2)+4300/((1+0.1)^3)+4500/((1+0.1)^4)+(4500*(1+0.02)/(0.1-0.02))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>320.975386171082</v>
       </c>
-      <c r="E11" s="57" t="n">
+      <c r="E11" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.1)^1)+4100/((1+0.1)^2)+4300/((1+0.1)^3)+4500/((1+0.1)^4)+(4500*(1+0.025)/(0.1-0.025))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>338.695074871591</v>
       </c>
-      <c r="F11" s="57" t="n">
+      <c r="F11" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.1)^1)+4100/((1+0.1)^2)+4300/((1+0.1)^3)+4500/((1+0.1)^4)+(4500*(1+0.03)/(0.1-0.03))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>358.946147672173</v>
       </c>
-      <c r="G11" s="57" t="n">
+      <c r="G11" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.1)^1)+4100/((1+0.1)^2)+4300/((1+0.1)^3)+4500/((1+0.1)^4)+(4500*(1+0.035)/(0.1-0.035))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>382.312770134382</v>
       </c>
-      <c r="H11" s="57" t="n">
+      <c r="H11" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.1)^1)+4100/((1+0.1)^2)+4300/((1+0.1)^3)+4500/((1+0.1)^4)+(4500*(1+0.04)/(0.1-0.04))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>409.573829673627</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="56" t="n">
+      <c r="B12" s="81" t="n">
         <v>0.105</v>
       </c>
-      <c r="C12" s="57" t="n">
+      <c r="C12" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.105)^1)+4100/((1+0.105)^2)+4300/((1+0.105)^3)+4500/((1+0.105)^4)+(4500*(1+0.015)/(0.105-0.015))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>287.684573666457</v>
       </c>
-      <c r="D12" s="57" t="n">
+      <c r="D12" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.105)^1)+4100/((1+0.105)^2)+4300/((1+0.105)^3)+4500/((1+0.105)^4)+(4500*(1+0.02)/(0.105-0.02))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>301.394563242069</v>
       </c>
-      <c r="E12" s="57" t="n">
+      <c r="E12" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.105)^1)+4100/((1+0.105)^2)+4300/((1+0.105)^3)+4500/((1+0.105)^4)+(4500*(1+0.025)/(0.105-0.025))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>316.818301514632</v>
       </c>
-      <c r="F12" s="57" t="n">
+      <c r="F12" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.105)^1)+4100/((1+0.105)^2)+4300/((1+0.105)^3)+4500/((1+0.105)^4)+(4500*(1+0.03)/(0.105-0.03))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>334.298538223538</v>
       </c>
-      <c r="G12" s="57" t="n">
+      <c r="G12" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.105)^1)+4100/((1+0.105)^2)+4300/((1+0.105)^3)+4500/((1+0.105)^4)+(4500*(1+0.035)/(0.105-0.035))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>354.275951605143</v>
       </c>
-      <c r="H12" s="57" t="n">
+      <c r="H12" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.105)^1)+4100/((1+0.105)^2)+4300/((1+0.105)^3)+4500/((1+0.105)^4)+(4500*(1+0.04)/(0.105-0.04))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>377.326813199304</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="56" t="n">
+      <c r="B13" s="81" t="n">
         <v>0.11</v>
       </c>
-      <c r="C13" s="57" t="n">
+      <c r="C13" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.11)^1)+4100/((1+0.11)^2)+4300/((1+0.11)^3)+4500/((1+0.11)^4)+(4500*(1+0.015)/(0.11-0.015))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>271.890437476961</v>
       </c>
-      <c r="D13" s="57" t="n">
+      <c r="D13" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.11)^1)+4100/((1+0.11)^2)+4300/((1+0.11)^3)+4500/((1+0.11)^4)+(4500*(1+0.02)/(0.11-0.02))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>283.992247826199</v>
       </c>
-      <c r="E13" s="57" t="n">
+      <c r="E13" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.11)^1)+4100/((1+0.11)^2)+4300/((1+0.11)^3)+4500/((1+0.11)^4)+(4500*(1+0.025)/(0.11-0.025))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>297.517800569465</v>
       </c>
-      <c r="F13" s="57" t="n">
+      <c r="F13" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.11)^1)+4100/((1+0.11)^2)+4300/((1+0.11)^3)+4500/((1+0.11)^4)+(4500*(1+0.03)/(0.11-0.03))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>312.734047405639</v>
       </c>
-      <c r="G13" s="57" t="n">
+      <c r="G13" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.11)^1)+4100/((1+0.11)^2)+4300/((1+0.11)^3)+4500/((1+0.11)^4)+(4500*(1+0.035)/(0.11-0.035))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>329.979127153303</v>
       </c>
-      <c r="H13" s="57" t="n">
+      <c r="H13" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.11)^1)+4100/((1+0.11)^2)+4300/((1+0.11)^3)+4500/((1+0.11)^4)+(4500*(1+0.04)/(0.11-0.04))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>349.687789722062</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="56" t="n">
+      <c r="B14" s="81" t="n">
         <v>0.12</v>
       </c>
-      <c r="C14" s="57" t="n">
+      <c r="C14" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.12)^1)+4100/((1+0.12)^2)+4300/((1+0.12)^3)+4500/((1+0.12)^4)+(4500*(1+0.015)/(0.12-0.015))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>244.823112388968</v>
       </c>
-      <c r="D14" s="57" t="n">
+      <c r="D14" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.12)^1)+4100/((1+0.12)^2)+4300/((1+0.12)^3)+4500/((1+0.12)^4)+(4500*(1+0.02)/(0.12-0.02))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>254.415838100739</v>
       </c>
-      <c r="E14" s="57" t="n">
+      <c r="E14" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.12)^1)+4100/((1+0.12)^2)+4300/((1+0.12)^3)+4500/((1+0.12)^4)+(4500*(1+0.025)/(0.12-0.025))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>265.018324413749</v>
       </c>
-      <c r="F14" s="57" t="n">
+      <c r="F14" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.12)^1)+4100/((1+0.12)^2)+4300/((1+0.12)^3)+4500/((1+0.12)^4)+(4500*(1+0.03)/(0.12-0.03))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>276.798864761538</v>
       </c>
-      <c r="G14" s="57" t="n">
+      <c r="G14" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.12)^1)+4100/((1+0.12)^2)+4300/((1+0.12)^3)+4500/((1+0.12)^4)+(4500*(1+0.035)/(0.12-0.035))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>289.965351032596</v>
       </c>
-      <c r="H14" s="57" t="n">
+      <c r="H14" s="82" t="n">
         <f aca="false">IFERROR((3800/((1+0.12)^1)+4100/((1+0.12)^2)+4300/((1+0.12)^3)+4500/((1+0.12)^4)+(4500*(1+0.04)/(0.12-0.04))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>304.777648087537</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="58" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
+      <c r="B18" s="83" t="s">
+        <v>241</v>
+      </c>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="60" t="n">
+      <c r="B19" s="84" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" s="85" t="n">
         <v>0.015</v>
       </c>
-      <c r="D19" s="60" t="n">
+      <c r="D19" s="85" t="n">
         <v>0.02</v>
       </c>
-      <c r="E19" s="60" t="n">
+      <c r="E19" s="85" t="n">
         <v>0.025</v>
       </c>
-      <c r="F19" s="60" t="n">
+      <c r="F19" s="85" t="n">
         <v>0.03</v>
       </c>
-      <c r="G19" s="60" t="n">
+      <c r="G19" s="85" t="n">
         <v>0.035</v>
       </c>
-      <c r="H19" s="60" t="n">
+      <c r="H19" s="85" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="60" t="n">
+      <c r="B20" s="85" t="n">
         <v>0.075</v>
       </c>
-      <c r="C20" s="57" t="n">
+      <c r="C20" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.075)^1)+5800/((1+0.075)^2)+6200/((1+0.075)^3)+6600/((1+0.075)^4)+(6600*(1+0.015)/(0.075-0.015))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>642.091551133546</v>
       </c>
-      <c r="D20" s="57" t="n">
+      <c r="D20" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.075)^1)+5800/((1+0.075)^2)+6200/((1+0.075)^3)+6600/((1+0.075)^4)+(6600*(1+0.02)/(0.075-0.02))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>692.7180020461</v>
       </c>
-      <c r="E20" s="57" t="n">
+      <c r="E20" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.075)^1)+5800/((1+0.075)^2)+6200/((1+0.075)^3)+6600/((1+0.075)^4)+(6600*(1+0.025)/(0.075-0.025))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>753.469743141164</v>
       </c>
-      <c r="F20" s="57" t="n">
+      <c r="F20" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.075)^1)+5800/((1+0.075)^2)+6200/((1+0.075)^3)+6600/((1+0.075)^4)+(6600*(1+0.03)/(0.075-0.03))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>827.721871146243</v>
       </c>
-      <c r="G20" s="57" t="n">
+      <c r="G20" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.075)^1)+5800/((1+0.075)^2)+6200/((1+0.075)^3)+6600/((1+0.075)^4)+(6600*(1+0.035)/(0.075-0.035))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>920.537031152591</v>
       </c>
-      <c r="H20" s="57" t="n">
+      <c r="H20" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.075)^1)+5800/((1+0.075)^2)+6200/((1+0.075)^3)+6600/((1+0.075)^4)+(6600*(1+0.04)/(0.075-0.04))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>1039.87080830361</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="60" t="n">
+      <c r="B21" s="85" t="n">
         <v>0.085</v>
       </c>
-      <c r="C21" s="57" t="n">
+      <c r="C21" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.085)^1)+5800/((1+0.085)^2)+6200/((1+0.085)^3)+6600/((1+0.085)^4)+(6600*(1+0.015)/(0.085-0.015))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>547.739288568662</v>
       </c>
-      <c r="D21" s="57" t="n">
+      <c r="D21" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.085)^1)+5800/((1+0.085)^2)+6200/((1+0.085)^3)+6600/((1+0.085)^4)+(6600*(1+0.02)/(0.085-0.02))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>583.451455612984</v>
       </c>
-      <c r="E21" s="57" t="n">
+      <c r="E21" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.085)^1)+5800/((1+0.085)^2)+6200/((1+0.085)^3)+6600/((1+0.085)^4)+(6600*(1+0.025)/(0.085-0.025))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>625.115650498025</v>
       </c>
-      <c r="F21" s="57" t="n">
+      <c r="F21" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.085)^1)+5800/((1+0.085)^2)+6200/((1+0.085)^3)+6600/((1+0.085)^4)+(6600*(1+0.03)/(0.085-0.03))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>674.355153543982</v>
       </c>
-      <c r="G21" s="57" t="n">
+      <c r="G21" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.085)^1)+5800/((1+0.085)^2)+6200/((1+0.085)^3)+6600/((1+0.085)^4)+(6600*(1+0.035)/(0.085-0.035))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>733.442557199132</v>
       </c>
-      <c r="H21" s="57" t="n">
+      <c r="H21" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.085)^1)+5800/((1+0.085)^2)+6200/((1+0.085)^3)+6600/((1+0.085)^4)+(6600*(1+0.04)/(0.085-0.04))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>805.66049499987</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="60" t="n">
+      <c r="B22" s="85" t="n">
         <v>0.095</v>
       </c>
-      <c r="C22" s="57" t="n">
+      <c r="C22" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.095)^1)+5800/((1+0.095)^2)+6200/((1+0.095)^3)+6600/((1+0.095)^4)+(6600*(1+0.015)/(0.095-0.015))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>477.011438198388</v>
       </c>
-      <c r="D22" s="57" t="n">
+      <c r="D22" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.095)^1)+5800/((1+0.095)^2)+6200/((1+0.095)^3)+6600/((1+0.095)^4)+(6600*(1+0.02)/(0.095-0.02))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>503.35795506949</v>
       </c>
-      <c r="E22" s="57" t="n">
+      <c r="E22" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.095)^1)+5800/((1+0.095)^2)+6200/((1+0.095)^3)+6600/((1+0.095)^4)+(6600*(1+0.025)/(0.095-0.025))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>533.468260065035</v>
       </c>
-      <c r="F22" s="57" t="n">
+      <c r="F22" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.095)^1)+5800/((1+0.095)^2)+6200/((1+0.095)^3)+6600/((1+0.095)^4)+(6600*(1+0.03)/(0.095-0.03))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>568.210919675279</v>
       </c>
-      <c r="G22" s="57" t="n">
+      <c r="G22" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.095)^1)+5800/((1+0.095)^2)+6200/((1+0.095)^3)+6600/((1+0.095)^4)+(6600*(1+0.035)/(0.095-0.035))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>608.744022553898</v>
       </c>
-      <c r="H22" s="57" t="n">
+      <c r="H22" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.095)^1)+5800/((1+0.095)^2)+6200/((1+0.095)^3)+6600/((1+0.095)^4)+(6600*(1+0.04)/(0.095-0.04))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>656.646780501356</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="60" t="n">
+      <c r="B23" s="85" t="n">
         <v>0.1</v>
       </c>
-      <c r="C23" s="57" t="n">
+      <c r="C23" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.1)^1)+5800/((1+0.1)^2)+6200/((1+0.1)^3)+6600/((1+0.1)^4)+(6600*(1+0.015)/(0.1-0.015))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>447.900612976149</v>
       </c>
-      <c r="D23" s="57" t="n">
+      <c r="D23" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.1)^1)+5800/((1+0.1)^2)+6200/((1+0.1)^3)+6600/((1+0.1)^4)+(6600*(1+0.02)/(0.1-0.02))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>470.831974823866</v>
       </c>
-      <c r="E23" s="57" t="n">
+      <c r="E23" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.1)^1)+5800/((1+0.1)^2)+6200/((1+0.1)^3)+6600/((1+0.1)^4)+(6600*(1+0.025)/(0.1-0.025))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>496.820851584612</v>
       </c>
-      <c r="F23" s="57" t="n">
+      <c r="F23" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.1)^1)+5800/((1+0.1)^2)+6200/((1+0.1)^3)+6600/((1+0.1)^4)+(6600*(1+0.03)/(0.1-0.03))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>526.522425025466</v>
       </c>
-      <c r="G23" s="57" t="n">
+      <c r="G23" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.1)^1)+5800/((1+0.1)^2)+6200/((1+0.1)^3)+6600/((1+0.1)^4)+(6600*(1+0.035)/(0.1-0.035))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>560.793471303373</v>
       </c>
-      <c r="H23" s="57" t="n">
+      <c r="H23" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.1)^1)+5800/((1+0.1)^2)+6200/((1+0.1)^3)+6600/((1+0.1)^4)+(6600*(1+0.04)/(0.1-0.04))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>600.776358627598</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="60" t="n">
+      <c r="B24" s="85" t="n">
         <v>0.105</v>
       </c>
-      <c r="C24" s="57" t="n">
+      <c r="C24" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.105)^1)+5800/((1+0.105)^2)+6200/((1+0.105)^3)+6600/((1+0.105)^4)+(6600*(1+0.015)/(0.105-0.015))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>422.031931724467</v>
       </c>
-      <c r="D24" s="57" t="n">
+      <c r="D24" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.105)^1)+5800/((1+0.105)^2)+6200/((1+0.105)^3)+6600/((1+0.105)^4)+(6600*(1+0.02)/(0.105-0.02))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>442.139916435364</v>
       </c>
-      <c r="E24" s="57" t="n">
+      <c r="E24" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.105)^1)+5800/((1+0.105)^2)+6200/((1+0.105)^3)+6600/((1+0.105)^4)+(6600*(1+0.025)/(0.105-0.025))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>464.761399235124</v>
       </c>
-      <c r="F24" s="57" t="n">
+      <c r="F24" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.105)^1)+5800/((1+0.105)^2)+6200/((1+0.105)^3)+6600/((1+0.105)^4)+(6600*(1+0.03)/(0.105-0.03))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>490.399079741518</v>
       </c>
-      <c r="G24" s="57" t="n">
+      <c r="G24" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.105)^1)+5800/((1+0.105)^2)+6200/((1+0.105)^3)+6600/((1+0.105)^4)+(6600*(1+0.035)/(0.105-0.035))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>519.69928603454</v>
       </c>
-      <c r="H24" s="57" t="n">
+      <c r="H24" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.105)^1)+5800/((1+0.105)^2)+6200/((1+0.105)^3)+6600/((1+0.105)^4)+(6600*(1+0.04)/(0.105-0.04))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>553.507216372642</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="60" t="n">
+      <c r="B25" s="85" t="n">
         <v>0.11</v>
       </c>
-      <c r="C25" s="57" t="n">
+      <c r="C25" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.11)^1)+5800/((1+0.11)^2)+6200/((1+0.11)^3)+6600/((1+0.11)^4)+(6600*(1+0.015)/(0.11-0.015))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>398.893336374383</v>
       </c>
-      <c r="D25" s="57" t="n">
+      <c r="D25" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.11)^1)+5800/((1+0.11)^2)+6200/((1+0.11)^3)+6600/((1+0.11)^4)+(6600*(1+0.02)/(0.11-0.02))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>416.642658219932</v>
       </c>
-      <c r="E25" s="57" t="n">
+      <c r="E25" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.11)^1)+5800/((1+0.11)^2)+6200/((1+0.11)^3)+6600/((1+0.11)^4)+(6600*(1+0.025)/(0.11-0.025))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>436.480135576721</v>
       </c>
-      <c r="F25" s="57" t="n">
+      <c r="F25" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.11)^1)+5800/((1+0.11)^2)+6200/((1+0.11)^3)+6600/((1+0.11)^4)+(6600*(1+0.03)/(0.11-0.03))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>458.79729760311</v>
       </c>
-      <c r="G25" s="57" t="n">
+      <c r="G25" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.11)^1)+5800/((1+0.11)^2)+6200/((1+0.11)^3)+6600/((1+0.11)^4)+(6600*(1+0.035)/(0.11-0.035))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>484.090081233017</v>
       </c>
-      <c r="H25" s="57" t="n">
+      <c r="H25" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.11)^1)+5800/((1+0.11)^2)+6200/((1+0.11)^3)+6600/((1+0.11)^4)+(6600*(1+0.04)/(0.11-0.04))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>512.996119667197</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="60" t="n">
+      <c r="B26" s="85" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="57" t="n">
+      <c r="C26" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.12)^1)+5800/((1+0.12)^2)+6200/((1+0.12)^3)+6600/((1+0.12)^4)+(6600*(1+0.015)/(0.12-0.015))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>359.245860935826</v>
       </c>
-      <c r="D26" s="57" t="n">
+      <c r="D26" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.12)^1)+5800/((1+0.12)^2)+6200/((1+0.12)^3)+6600/((1+0.12)^4)+(6600*(1+0.02)/(0.12-0.02))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>373.315191979757</v>
       </c>
-      <c r="E26" s="57" t="n">
+      <c r="E26" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.12)^1)+5800/((1+0.12)^2)+6200/((1+0.12)^3)+6600/((1+0.12)^4)+(6600*(1+0.025)/(0.12-0.025))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>388.865505238838</v>
       </c>
-      <c r="F26" s="57" t="n">
+      <c r="F26" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.12)^1)+5800/((1+0.12)^2)+6200/((1+0.12)^3)+6600/((1+0.12)^4)+(6600*(1+0.03)/(0.12-0.03))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>406.143631082262</v>
       </c>
-      <c r="G26" s="57" t="n">
+      <c r="G26" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.12)^1)+5800/((1+0.12)^2)+6200/((1+0.12)^3)+6600/((1+0.12)^4)+(6600*(1+0.035)/(0.12-0.035))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>425.454477613148</v>
       </c>
-      <c r="H26" s="57" t="n">
+      <c r="H26" s="82" t="n">
         <f aca="false">IFERROR((5200/((1+0.12)^1)+5800/((1+0.12)^2)+6200/((1+0.12)^3)+6600/((1+0.12)^4)+(6600*(1+0.04)/(0.12-0.04))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>447.179179960394</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
+      <c r="B30" s="86" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="62" t="s">
-        <v>178</v>
-      </c>
-      <c r="C31" s="63" t="n">
+      <c r="B31" s="87" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" s="88" t="n">
         <v>0.015</v>
       </c>
-      <c r="D31" s="63" t="n">
+      <c r="D31" s="88" t="n">
         <v>0.02</v>
       </c>
-      <c r="E31" s="63" t="n">
+      <c r="E31" s="88" t="n">
         <v>0.025</v>
       </c>
-      <c r="F31" s="63" t="n">
+      <c r="F31" s="88" t="n">
         <v>0.03</v>
       </c>
-      <c r="G31" s="63" t="n">
+      <c r="G31" s="88" t="n">
         <v>0.035</v>
       </c>
-      <c r="H31" s="63" t="n">
+      <c r="H31" s="88" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="63" t="n">
+      <c r="B32" s="88" t="n">
         <v>0.075</v>
       </c>
-      <c r="C32" s="57" t="n">
+      <c r="C32" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.075)^1)+7800/((1+0.075)^2)+8500/((1+0.075)^3)+9200/((1+0.075)^4)+(9200*(1+0.015)/(0.075-0.015))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>893.362439851096</v>
       </c>
-      <c r="D32" s="57" t="n">
+      <c r="D32" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.075)^1)+7800/((1+0.075)^2)+8500/((1+0.075)^3)+9200/((1+0.075)^4)+(9200*(1+0.02)/(0.075-0.02))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>963.932644153444</v>
       </c>
-      <c r="E32" s="57" t="n">
+      <c r="E32" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.075)^1)+7800/((1+0.075)^2)+8500/((1+0.075)^3)+9200/((1+0.075)^4)+(9200*(1+0.025)/(0.075-0.025))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>1048.61688931626</v>
       </c>
-      <c r="F32" s="57" t="n">
+      <c r="F32" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.075)^1)+7800/((1+0.075)^2)+8500/((1+0.075)^3)+9200/((1+0.075)^4)+(9200*(1+0.03)/(0.075-0.03))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>1152.11985562637</v>
       </c>
-      <c r="G32" s="57" t="n">
+      <c r="G32" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.075)^1)+7800/((1+0.075)^2)+8500/((1+0.075)^3)+9200/((1+0.075)^4)+(9200*(1+0.035)/(0.075-0.035))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>1281.49856351401</v>
       </c>
-      <c r="H32" s="57" t="n">
+      <c r="H32" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.075)^1)+7800/((1+0.075)^2)+8500/((1+0.075)^3)+9200/((1+0.075)^4)+(9200*(1+0.04)/(0.075-0.04))/((1+0.075)^4)-1300)/159,"N/A")</f>
         <v>1447.8426165124</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="63" t="n">
+      <c r="B33" s="88" t="n">
         <v>0.085</v>
       </c>
-      <c r="C33" s="57" t="n">
+      <c r="C33" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.085)^1)+7800/((1+0.085)^2)+8500/((1+0.085)^3)+9200/((1+0.085)^4)+(9200*(1+0.015)/(0.085-0.015))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>761.913485008059</v>
       </c>
-      <c r="D33" s="57" t="n">
+      <c r="D33" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.085)^1)+7800/((1+0.085)^2)+8500/((1+0.085)^3)+9200/((1+0.085)^4)+(9200*(1+0.02)/(0.085-0.02))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>811.694081494082</v>
       </c>
-      <c r="E33" s="57" t="n">
+      <c r="E33" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.085)^1)+7800/((1+0.085)^2)+8500/((1+0.085)^3)+9200/((1+0.085)^4)+(9200*(1+0.025)/(0.085-0.025))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>869.77144406111</v>
       </c>
-      <c r="F33" s="57" t="n">
+      <c r="F33" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.085)^1)+7800/((1+0.085)^2)+8500/((1+0.085)^3)+9200/((1+0.085)^4)+(9200*(1+0.03)/(0.085-0.03))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>938.408327094869</v>
       </c>
-      <c r="G33" s="57" t="n">
+      <c r="G33" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.085)^1)+7800/((1+0.085)^2)+8500/((1+0.085)^3)+9200/((1+0.085)^4)+(9200*(1+0.035)/(0.085-0.035))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>1020.77258673538</v>
       </c>
-      <c r="H33" s="57" t="n">
+      <c r="H33" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.085)^1)+7800/((1+0.085)^2)+8500/((1+0.085)^3)+9200/((1+0.085)^4)+(9200*(1+0.04)/(0.085-0.04))/((1+0.085)^4)-1300)/159,"N/A")</f>
         <v>1121.44001518489</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="63" t="n">
+      <c r="B34" s="88" t="n">
         <v>0.095</v>
       </c>
-      <c r="C34" s="57" t="n">
+      <c r="C34" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.095)^1)+7800/((1+0.095)^2)+8500/((1+0.095)^3)+9200/((1+0.095)^4)+(9200*(1+0.015)/(0.095-0.015))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>663.393596541707</v>
       </c>
-      <c r="D34" s="57" t="n">
+      <c r="D34" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.095)^1)+7800/((1+0.095)^2)+8500/((1+0.095)^3)+9200/((1+0.095)^4)+(9200*(1+0.02)/(0.095-0.02))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>700.119044301425</v>
       </c>
-      <c r="E34" s="57" t="n">
+      <c r="E34" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.095)^1)+7800/((1+0.095)^2)+8500/((1+0.095)^3)+9200/((1+0.095)^4)+(9200*(1+0.025)/(0.095-0.025))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>742.090984598246</v>
       </c>
-      <c r="F34" s="57" t="n">
+      <c r="F34" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.095)^1)+7800/((1+0.095)^2)+8500/((1+0.095)^3)+9200/((1+0.095)^4)+(9200*(1+0.03)/(0.095-0.03))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>790.520146479192</v>
       </c>
-      <c r="G34" s="57" t="n">
+      <c r="G34" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.095)^1)+7800/((1+0.095)^2)+8500/((1+0.095)^3)+9200/((1+0.095)^4)+(9200*(1+0.035)/(0.095-0.035))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>847.020835340297</v>
       </c>
-      <c r="H34" s="57" t="n">
+      <c r="H34" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.095)^1)+7800/((1+0.095)^2)+8500/((1+0.095)^3)+9200/((1+0.095)^4)+(9200*(1+0.04)/(0.095-0.04))/((1+0.095)^4)-1300)/159,"N/A")</f>
         <v>913.794376721602</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="63" t="n">
+      <c r="B35" s="88" t="n">
         <v>0.1</v>
       </c>
-      <c r="C35" s="57" t="n">
+      <c r="C35" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.1)^1)+7800/((1+0.1)^2)+8500/((1+0.1)^3)+9200/((1+0.1)^4)+(9200*(1+0.015)/(0.1-0.015))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>622.849392652458</v>
       </c>
-      <c r="D35" s="57" t="n">
+      <c r="D35" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.1)^1)+7800/((1+0.1)^2)+8500/((1+0.1)^3)+9200/((1+0.1)^4)+(9200*(1+0.02)/(0.1-0.02))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>654.81432128867</v>
       </c>
-      <c r="E35" s="57" t="n">
+      <c r="E35" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.1)^1)+7800/((1+0.1)^2)+8500/((1+0.1)^3)+9200/((1+0.1)^4)+(9200*(1+0.025)/(0.1-0.025))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>691.04124040971</v>
       </c>
-      <c r="F35" s="57" t="n">
+      <c r="F35" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.1)^1)+7800/((1+0.1)^2)+8500/((1+0.1)^3)+9200/((1+0.1)^4)+(9200*(1+0.03)/(0.1-0.03))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>732.4434336909</v>
       </c>
-      <c r="G35" s="57" t="n">
+      <c r="G35" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.1)^1)+7800/((1+0.1)^2)+8500/((1+0.1)^3)+9200/((1+0.1)^4)+(9200*(1+0.035)/(0.1-0.035))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>780.215195169195</v>
       </c>
-      <c r="H35" s="57" t="n">
+      <c r="H35" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.1)^1)+7800/((1+0.1)^2)+8500/((1+0.1)^3)+9200/((1+0.1)^4)+(9200*(1+0.04)/(0.1-0.04))/((1+0.1)^4)-1300)/159,"N/A")</f>
         <v>835.948916893872</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="63" t="n">
+      <c r="B36" s="88" t="n">
         <v>0.105</v>
       </c>
-      <c r="C36" s="57" t="n">
+      <c r="C36" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.105)^1)+7800/((1+0.105)^2)+8500/((1+0.105)^3)+9200/((1+0.105)^4)+(9200*(1+0.015)/(0.105-0.015))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>586.824084587449</v>
       </c>
-      <c r="D36" s="57" t="n">
+      <c r="D36" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.105)^1)+7800/((1+0.105)^2)+8500/((1+0.105)^3)+9200/((1+0.105)^4)+(9200*(1+0.02)/(0.105-0.02))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>614.8533966087</v>
       </c>
-      <c r="E36" s="57" t="n">
+      <c r="E36" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.105)^1)+7800/((1+0.105)^2)+8500/((1+0.105)^3)+9200/((1+0.105)^4)+(9200*(1+0.025)/(0.105-0.025))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>646.386372632607</v>
       </c>
-      <c r="F36" s="57" t="n">
+      <c r="F36" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.105)^1)+7800/((1+0.105)^2)+8500/((1+0.105)^3)+9200/((1+0.105)^4)+(9200*(1+0.03)/(0.105-0.03))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>682.123745459702</v>
       </c>
-      <c r="G36" s="57" t="n">
+      <c r="G36" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.105)^1)+7800/((1+0.105)^2)+8500/((1+0.105)^3)+9200/((1+0.105)^4)+(9200*(1+0.035)/(0.105-0.035))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>722.966457262096</v>
       </c>
-      <c r="H36" s="57" t="n">
+      <c r="H36" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.105)^1)+7800/((1+0.105)^2)+8500/((1+0.105)^3)+9200/((1+0.105)^4)+(9200*(1+0.04)/(0.105-0.04))/((1+0.105)^4)-1300)/159,"N/A")</f>
         <v>770.092663187936</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="63" t="n">
+      <c r="B37" s="88" t="n">
         <v>0.11</v>
       </c>
-      <c r="C37" s="57" t="n">
+      <c r="C37" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.11)^1)+7800/((1+0.11)^2)+8500/((1+0.11)^3)+9200/((1+0.11)^4)+(9200*(1+0.015)/(0.11-0.015))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>554.603902905335</v>
       </c>
-      <c r="D37" s="57" t="n">
+      <c r="D37" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.11)^1)+7800/((1+0.11)^2)+8500/((1+0.11)^3)+9200/((1+0.11)^4)+(9200*(1+0.02)/(0.11-0.02))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>579.345381841555</v>
       </c>
-      <c r="E37" s="57" t="n">
+      <c r="E37" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.11)^1)+7800/((1+0.11)^2)+8500/((1+0.11)^3)+9200/((1+0.11)^4)+(9200*(1+0.025)/(0.11-0.025))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>606.997623005565</v>
       </c>
-      <c r="F37" s="57" t="n">
+      <c r="F37" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.11)^1)+7800/((1+0.11)^2)+8500/((1+0.11)^3)+9200/((1+0.11)^4)+(9200*(1+0.03)/(0.11-0.03))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>638.106394315076</v>
       </c>
-      <c r="G37" s="57" t="n">
+      <c r="G37" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.11)^1)+7800/((1+0.11)^2)+8500/((1+0.11)^3)+9200/((1+0.11)^4)+(9200*(1+0.035)/(0.11-0.035))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>673.363001799189</v>
       </c>
-      <c r="H37" s="57" t="n">
+      <c r="H37" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.11)^1)+7800/((1+0.11)^2)+8500/((1+0.11)^3)+9200/((1+0.11)^4)+(9200*(1+0.04)/(0.11-0.04))/((1+0.11)^4)-1300)/159,"N/A")</f>
         <v>713.656267495318</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="63" t="n">
+      <c r="B38" s="88" t="n">
         <v>0.12</v>
       </c>
-      <c r="C38" s="57" t="n">
+      <c r="C38" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.12)^1)+7800/((1+0.12)^2)+8500/((1+0.12)^3)+9200/((1+0.12)^4)+(9200*(1+0.015)/(0.12-0.015))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>499.403650001266</v>
       </c>
-      <c r="D38" s="57" t="n">
+      <c r="D38" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.12)^1)+7800/((1+0.12)^2)+8500/((1+0.12)^3)+9200/((1+0.12)^4)+(9200*(1+0.02)/(0.12-0.02))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>519.015444789776</v>
       </c>
-      <c r="E38" s="57" t="n">
+      <c r="E38" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.12)^1)+7800/((1+0.12)^2)+8500/((1+0.12)^3)+9200/((1+0.12)^4)+(9200*(1+0.025)/(0.12-0.025))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>540.691639029707</v>
       </c>
-      <c r="F38" s="57" t="n">
+      <c r="F38" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.12)^1)+7800/((1+0.12)^2)+8500/((1+0.12)^3)+9200/((1+0.12)^4)+(9200*(1+0.03)/(0.12-0.03))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>564.776299296298</v>
       </c>
-      <c r="G38" s="57" t="n">
+      <c r="G38" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.12)^1)+7800/((1+0.12)^2)+8500/((1+0.12)^3)+9200/((1+0.12)^4)+(9200*(1+0.035)/(0.12-0.035))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>591.694449006017</v>
       </c>
-      <c r="H38" s="57" t="n">
+      <c r="H38" s="82" t="n">
         <f aca="false">IFERROR((6800/((1+0.12)^1)+7800/((1+0.12)^2)+8500/((1+0.12)^3)+9200/((1+0.12)^4)+(9200*(1+0.04)/(0.12-0.04))/((1+0.12)^4)-1300)/159,"N/A")</f>
         <v>621.977367429451</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="64" t="s">
-        <v>181</v>
-      </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
-      <c r="I43" s="64"/>
+      <c r="B43" s="89" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="89"/>
+      <c r="D43" s="89"/>
+      <c r="E43" s="89"/>
+      <c r="F43" s="89"/>
+      <c r="G43" s="89"/>
+      <c r="H43" s="89"/>
+      <c r="I43" s="89"/>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="64"/>
-      <c r="C44" s="64"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="64"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="89"/>
+      <c r="H44" s="89"/>
+      <c r="I44" s="89"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="35"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
+      <c r="B46" s="59" t="s">
+        <v>244</v>
+      </c>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="7">
